--- a/output/graficos_regionales/plot_regional_serie_i_ingr_s_2023_los_lagos.xlsx
+++ b/output/graficos_regionales/plot_regional_serie_i_ingr_s_2023_los_lagos.xlsx
@@ -78,7 +78,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-28 16:38</t>
+    <t xml:space="preserve">2026-10-05 01:59</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>687597.12</v>
+        <v>687597.13</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>795057.75</v>
@@ -546,7 +546,7 @@
         <v>8</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>809153.62</v>
+        <v>809153.63</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>909214.94</v>
@@ -590,7 +590,7 @@
         <v>12</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>979678.12</v>
+        <v>979678.13</v>
       </c>
       <c r="C11" s="2" t="n">
         <v>1104330.75</v>
@@ -604,7 +604,7 @@
         <v>1036574.5</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>1163774.62</v>
+        <v>1163774.63</v>
       </c>
     </row>
     <row r="13">
